--- a/survey_templates/045_philippine_history_quiz--survey_templates.xlsx
+++ b/survey_templates/045_philippine_history_quiz--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -528,7 +528,11 @@
           <t>introduction</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>This is the introduction page</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>yes</t>
@@ -548,10 +552,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>native_category</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please select your native category</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>yes</t>
@@ -566,15 +574,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>question_1</t>
+          <t>age</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>question_1</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please enter your age</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>yes</t>
@@ -589,15 +601,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>question_2</t>
+          <t>historical_periods</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>question_2</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>favorite_historical_periods</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Select your favorite historical periods</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>yes</t>
@@ -607,20 +623,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>date_of_birth</t>
+          <t>favorite_event</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>date_of_birth</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>favorite_event</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Please select your favorite historical event</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>yes</t>
@@ -630,46 +650,54 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>goals</t>
+          <t>birthdate</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>_goals</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>birthdate</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Please enter your birthdate</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>goals</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>short_term_goals</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Select your short-term goals</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -689,7 +717,11 @@
           <t>email</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Do you have an email?</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>yes</t>
@@ -712,7 +744,11 @@
           <t>phone</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Please enter your phone number</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>yes</t>
@@ -735,123 +771,12 @@
           <t>submit</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Please submit the form</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>goals</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>_goals</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>goals</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>_goals</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>goals</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>_goals</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>goals</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>_goals</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -868,12 +793,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -981,187 +906,187 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>historical_periods_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>pre-colonial_period</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>Pre-Colonial Period</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>historical_periods_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>spanish_colonial_era</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>Spanish Colonial Era</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>historical_periods_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>japanese_occupation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>Japanese Occupation</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>goals_choices</t>
+          <t>historical_periods_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>american_colonial_era</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>American Colonial Era</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>goals_choices</t>
+          <t>historical_periods_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>post-war_period</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>Post-War Period</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>goals_choices</t>
+          <t>historical_periods_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>contemporary_era</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>Contemporary Era</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>goals_choices</t>
+          <t>favorite_event_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>bataan_death_march</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>Bataan Death March</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>goals_choices</t>
+          <t>favorite_event_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>battle_of_mactan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>Battle of Mactan</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>goals_choices</t>
+          <t>favorite_event_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>discovery_of_the_bicol_region</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>Discovery of the Bicol Region</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>goals_choices</t>
+          <t>favorite_event_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>founding_of_the_republic_of_the_philippines</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>Founding of the Republic of the Philippines</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>goals_choices</t>
+          <t>favorite_event_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>philippine-american_war</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>Philippine-American War</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1098,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>personal_development</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>Personal Development</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1115,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>career_development</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>Career Development</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1132,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>social_contribution</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>Social Contribution</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1149,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>financial_security</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>Financial Security</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1166,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>travel_and_leisure</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>Travel and Leisure</t>
         </is>
       </c>
     </row>
@@ -1258,29 +1183,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>b</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>goals_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>c</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
